--- a/.claude/skills/hld-creator/artifacts/discovery/intune-government-discovery-pack.xlsx
+++ b/.claude/skills/hld-creator/artifacts/discovery/intune-government-discovery-pack.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Master question list, ~150 rows across 17 domains, each traced to an HLD section.</t>
+          <t>Master question list: 169 questions across 17 domains, each traced to an HLD section.</t>
         </is>
       </c>
     </row>
